--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO5" headerRowCount="1">
+  <autoFilter ref="A1:CO5"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,1055 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>4cc4b1372ca547f6</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:13.303229Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>66820</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.538216</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.04802</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="n"/>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n"/>
+      <c r="AD2" s="24" t="n"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-kbo-dbo-ltg-2026-08-02). Tie probability=0.0325.</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:11.923167Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>8151a1369adb4194</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:13.303229Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>66821</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.572182</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>-0.027818</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-lgo-sla-2026-08-02). Tie probability=0.0296.</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:12.387725Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>df7618754bf540d9</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:13.303229Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>66822</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.500344</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>-0.109031</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="n"/>
+      <c r="W4" s="26" t="n"/>
+      <c r="X4" s="26" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n"/>
+      <c r="AD4" s="24" t="n"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-kbo-ndc-kti-2026-08-02). Tie probability=0.0357.</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:12.841895Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>623c9d8815784f23</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:13.303229Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>66824</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.60172</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.10172</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="n"/>
+      <c r="W5" s="26" t="n"/>
+      <c r="X5" s="26" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n"/>
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5000 (market_slug=aec-kbo-kwt-hea-2026-08-02). Tie probability=0.0270.</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:13.303069Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -1578,12 +1578,12 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>4cc4b1372ca547f6</t>
+          <t>6b298622637b4852</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:13.303229Z</t>
+          <t>2026-08-02T08:20:39.643741Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
@@ -1628,23 +1628,23 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.538216</v>
+        <v>0.537313</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>0.04802</v>
+        <v>0.067829</v>
       </c>
       <c r="R2" s="26" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S2" s="29" t="n">
         <v>1</v>
@@ -1670,7 +1670,7 @@
       <c r="AD2" s="24" t="n"/>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-kbo-dbo-ltg-2026-08-02). Tie probability=0.0325.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-kbo-dbo-ltg-2026-08-02). Tie probability=0.0329.</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:11.923167Z</t>
+          <t>2026-08-02T08:20:38.172250Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1799,13 +1799,13 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
@@ -1839,12 +1839,12 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>8151a1369adb4194</t>
+          <t>a18447f9f3764884</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:13.303229Z</t>
+          <t>2026-08-02T08:20:39.643741Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
@@ -1898,11 +1898,11 @@
         <v>0.6</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.572182</v>
+        <v>0.571761</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>-0.027818</v>
+        <v>-0.028239</v>
       </c>
       <c r="R3" s="26" t="n">
         <v>6</v>
@@ -1931,7 +1931,7 @@
       <c r="AD3" s="24" t="n"/>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-lgo-sla-2026-08-02). Tie probability=0.0296.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-lgo-sla-2026-08-02). Tie probability=0.0299.</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:12.387725Z</t>
+          <t>2026-08-02T08:20:38.678859Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>df7618754bf540d9</t>
+          <t>9aae1bcd206c4cd9</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:13.303229Z</t>
+          <t>2026-08-02T08:20:39.643741Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
@@ -2159,11 +2159,11 @@
         <v>0.609375</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.500344</v>
+        <v>0.500454</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>-0.109031</v>
+        <v>-0.108921</v>
       </c>
       <c r="R4" s="26" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
       <c r="AD4" s="24" t="n"/>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-kbo-ndc-kti-2026-08-02). Tie probability=0.0357.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-kbo-ndc-kti-2026-08-02). Tie probability=0.0361.</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:12.841895Z</t>
+          <t>2026-08-02T08:20:39.168704Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>623c9d8815784f23</t>
+          <t>b812d36f9af4454f</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:13.303229Z</t>
+          <t>2026-08-02T08:20:39.643741Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
@@ -2411,23 +2411,23 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>2</v>
+        <v>1.961538</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.5</v>
+        <v>0.509804</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.60172</v>
+        <v>0.599423</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.10172</v>
+        <v>0.089619</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1.25</v>
@@ -2453,7 +2453,7 @@
       <c r="AD5" s="24" t="n"/>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.5000 (market_slug=aec-kbo-kwt-hea-2026-08-02). Tie probability=0.0270.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-kwt-hea-2026-08-02). Tie probability=0.0275.</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>5c2fb36d913b70cf75e2c1e869cc3c67839c1187c5108a5fd3706111ad5baae3</t>
+          <t>9ed13cfd8d860b2670f938484c3c659d864654d10d93ca38480a7e8d77633502</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:13.303069Z</t>
+          <t>2026-08-02T08:20:39.643606Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2582,13 +2582,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>2</v>
+        <v>1.961538</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.5</v>
+        <v>0.509804</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -1656,18 +1656,32 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:53:25.994801Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-kbo-dbo-ltg-2026-08-02). Tie probability=0.0329.</t>
@@ -1917,18 +1931,32 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>-0.2083</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:53:31.723233Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-lgo-sla-2026-08-02). Tie probability=0.0299.</t>
@@ -2439,18 +2467,32 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:53:37.329479Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-kwt-hea-2026-08-02). Tie probability=0.0275.</t>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO5" headerRowCount="1">
-  <autoFilter ref="A1:CO5"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP5" headerRowCount="1">
+  <autoFilter ref="A1:CP5"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO5"/>
+  <dimension ref="A1:CP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1849,6 +1856,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2124,6 +2132,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2385,6 +2394,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2660,6 +2670,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP5" headerRowCount="1">
-  <autoFilter ref="A1:CP5"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
+  <autoFilter ref="A1:CQ5"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP5"/>
+  <dimension ref="A1:CQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1857,6 +1864,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2133,6 +2141,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2395,6 +2404,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2671,6 +2681,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
-  <autoFilter ref="A1:CQ5"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR10" headerRowCount="1">
+  <autoFilter ref="A1:CR10"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ5"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1865,6 +1872,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2142,6 +2150,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2405,6 +2414,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2682,6 +2692,1347 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>82e9095226ef4d4d</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662874Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>68265</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.5790380000000001</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.188413</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.3900 (market_slug=aec-kbo-dbo-ndc-2026-08-04). Tie probability=0.0299.</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.155611Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>3d42a08544994bf4</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662874Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>68266</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.550713</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>-0.139689</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6900 (market_slug=aec-kbo-sls-ltg-2026-08-04). Tie probability=0.0325.</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.825209Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>3b94e7433b554d5d</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662874Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>68268</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.5638300000000001</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-kbo-lgo-khi-2026-08-04). Tie probability=0.0313.</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:28.469450Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>b0366f9bba48413a</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662874Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>68270</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.020885</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-kbo-sla-hea-2026-08-04). Tie probability=0.0288.</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194279Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>8b5fd89c6c904404</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662874Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>68271</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.539741</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.09921199999999999</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4400 (market_slug=aec-kbo-kti-kwt-2026-08-04). Tie probability=0.0335.</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>ed3011bd159f6231451a9fe0e125e5f3fe12152fa880d63d1c0f52c74fa66b4f</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.662825Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR10" headerRowCount="1">
-  <autoFilter ref="A1:CR10"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
+  <autoFilter ref="A1:CS10"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1873,6 +1880,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2151,6 +2159,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2415,6 +2424,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2693,6 +2703,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2956,7 +2967,8 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
-      <c r="CR6" s="24" t="inlineStr">
+      <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3043,18 +3055,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-0.2758</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:56.981607Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6900 (market_slug=aec-kbo-sls-ltg-2026-08-04). Tie probability=0.0325.</t>
@@ -3224,7 +3250,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3311,18 +3338,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-0.2059</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:57.054537Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-kbo-lgo-khi-2026-08-04). Tie probability=0.0313.</t>
@@ -3492,7 +3533,8 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
-      <c r="CR8" s="24" t="inlineStr">
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3579,18 +3621,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-0.1551</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:57.126892Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-kbo-sla-hea-2026-08-04). Tie probability=0.0288.</t>
@@ -3760,7 +3816,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4028,7 +4085,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
-  <autoFilter ref="A1:CS10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS15" headerRowCount="1">
+  <autoFilter ref="A1:CS15"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4092,6 +4092,1351 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>cc40a51fc9624e7a</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.5786289999999999</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.158461</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4200 (market_slug=aec-kbo-dbo-ndc-2026-08-05). Tie probability=0.0300.</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:48.171174Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>13b6204472b44df9</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.538431</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.051733</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-kbo-sls-ltg-2026-08-05). Tie probability=0.0336.</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.042489Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>1dc4333ded9742e4</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.539389</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.020158</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-kbo-kti-kwt-2026-08-05). Tie probability=0.0335.</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.843883Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>f8db5f75eff54bc7</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.578674</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>-0.041098</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-kbo-sla-hea-2026-08-05). Tie probability=0.0300.</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.877475Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>a6ba9cea53e7469c</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.573348</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.083152</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-kbo-lgo-khi-2026-08-05). Tie probability=0.0304.</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796672Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
-  <autoFilter ref="A1:CS10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS20" headerRowCount="1">
+  <autoFilter ref="A1:CS20"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$20)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$20)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4092,6 +4092,2766 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>cc40a51fc9624e7a</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.5786289999999999</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.158461</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4200 (market_slug=aec-kbo-dbo-ndc-2026-08-05). Tie probability=0.0300.</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:48.171174Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>13b6204472b44df9</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>69520</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.538431</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>-0.051733</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-kbo-sls-ltg-2026-08-05). Tie probability=0.0336.</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.042489Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>1dc4333ded9742e4</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.539389</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.020158</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-kbo-kti-kwt-2026-08-05). Tie probability=0.0335.</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.843883Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>f8db5f75eff54bc7</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>69522</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.578674</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>-0.041098</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-kbo-sla-hea-2026-08-05). Tie probability=0.0300.</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.877475Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>a6ba9cea53e7469c</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796720Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.573348</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.083152</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-kbo-lgo-khi-2026-08-05). Tie probability=0.0304.</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>42580816cbd4c4e1853d7ee970337b5714d38d677b257c76baa90b243516ed94</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.796672Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>bfeb4322bfe5401e</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448983Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>76203</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.528545</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.028545</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.043150Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5000 (market_slug=aec-kbo-sls-lgo-2026-08-12). Tie probability=0.0253.</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:31.891013Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>3ae7b9855c094bee</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448983Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>76204</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.541292</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>-0.008258</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>-0.0902</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.197035Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-kbo-dbo-hea-2026-08-12). Tie probability=0.0253.</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:32.786185Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>06b4cf4593c64031</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448983Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>76206</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.5977440000000001</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>-0.052606</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-0.289</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.313757Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6500 (market_slug=aec-kbo-ndc-kwt-2026-08-12). Tie probability=0.0253.</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.260921Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>afd2b18fdb004a35</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448983Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>76207</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.531537</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.07070799999999999</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.457044Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4600 (market_slug=aec-kbo-kti-sla-2026-08-12). Tie probability=0.0253.</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.722273Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>36507b73df7f4619</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448983Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>76208</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.5758490000000001</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.134296</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>-0.3699</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:25:33.580880Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7100 (market_slug=aec-kbo-khi-ltg-2026-08-12). Tie probability=0.0253.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>cc6ea1b83ff16d7501f49063575d9bfa76cd7001cbae8a5672014d3aa4ff1706</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.448940Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/kbo.xlsx
+++ b/data/research/kbo.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS20" headerRowCount="1">
-  <autoFilter ref="A1:CS20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
+  <autoFilter ref="A1:CS25"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$20)</f>
+        <f>COUNTA('Picks'!$A$2:$A$25)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$20)</f>
+        <f>SUM('Picks'!$BY$2:$BY$25)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS20"/>
+  <dimension ref="A1:CS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1689,21 +1689,21 @@
       </c>
       <c r="V2" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W2" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
       <c r="AC2" s="30" t="n">
-        <v>0.065</v>
+        <v>1.13</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
       </c>
       <c r="V3" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W3" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X3" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
       <c r="AC3" s="30" t="n">
-        <v>-0.2083</v>
+        <v>-1.25</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -2512,21 +2512,21 @@
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W5" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>-0.024</v>
+        <v>1.2019</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W7" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X7" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
       <c r="AC7" s="30" t="n">
-        <v>-0.2758</v>
+        <v>-1</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3343,21 +3343,21 @@
       </c>
       <c r="V8" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W8" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
       <c r="AC8" s="30" t="n">
-        <v>-0.2059</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W9" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
       <c r="AC9" s="30" t="n">
-        <v>-0.1551</v>
+        <v>-1.25</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -5523,21 +5523,21 @@
       </c>
       <c r="V16" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W16" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
       <c r="AC16" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5806,21 +5806,21 @@
       </c>
       <c r="V17" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W17" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X17" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
       <c r="AC17" s="30" t="n">
-        <v>-0.0902</v>
+        <v>-1</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -6089,21 +6089,21 @@
       </c>
       <c r="V18" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W18" s="26" t="n">
         <v>0</v>
       </c>
       <c r="X18" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
       <c r="AC18" s="30" t="n">
-        <v>-0.289</v>
+        <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6372,21 +6372,21 @@
       </c>
       <c r="V19" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W19" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
       <c r="AC19" s="30" t="n">
-        <v>0.08500000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="AG19" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH19" s="24" t="n"/>
@@ -6655,21 +6655,21 @@
       </c>
       <c r="V20" s="24" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W20" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X20" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
       <c r="AC20" s="30" t="n">
-        <v>-0.3699</v>
+        <v>-1.25</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AG20" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH20" s="24" t="n"/>
@@ -6852,6 +6852,1421 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>639d9dffcd6e41ed</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934569Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>77220</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.528176</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.077726</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:06:27.986483Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4500 (market_slug=aec-kbo-dbo-hea-2026-08-13). Tie probability=0.0260.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:34.898609Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>acc1c064ae934f16</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934569Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>77221</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.515911</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:06:28.130443Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-kbo-sls-lgo-2026-08-13). Tie probability=0.0260.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.524021Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>9eeaf5ce9c8d4cb1</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934569Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>77222</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.518728</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>-0.141136</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:06:28.251805Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-kbo-kti-sla-2026-08-13). Tie probability=0.0260.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.996158Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>35c360f2be8247f1</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934569Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.56116</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>-0.06847</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:06:28.375256Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-kbo-khi-ltg-2026-08-13). Tie probability=0.0260.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.470286Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>6ac39ae14c214e0f</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934569Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>77224</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.5823120000000001</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.051796</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:06:28.497691Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-kbo-ndc-kwt-2026-08-13). Tie probability=0.0260.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934402Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
